--- a/artfynd/A 23688-2026 artfynd.xlsx
+++ b/artfynd/A 23688-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389970</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389983</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389969</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389944</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389954</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389961</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389967</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389974</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389937</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389940</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389947</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389949</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389953</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389955</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389956</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389957</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2831,6 +2931,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389960</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2957,6 +3062,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389962</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3064,6 +3174,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389965</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3171,6 +3286,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389966</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3278,6 +3398,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389975</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3385,6 +3510,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389977</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3511,6 +3641,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389978</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3618,6 +3753,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389979</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3725,6 +3865,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389981</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3851,6 +3996,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389986</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3977,6 +4127,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389989</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4103,6 +4258,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389991</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4218,6 +4378,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389943</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4325,6 +4490,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389958</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4432,6 +4602,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389948</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4539,6 +4714,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389950</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4654,6 +4834,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389939</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4769,6 +4954,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389951</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4884,6 +5074,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389968</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4999,6 +5194,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389984</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5122,6 +5322,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389992</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5242,6 +5447,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389941</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5362,6 +5572,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389988</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5482,6 +5697,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389993</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5597,6 +5817,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389959</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5712,6 +5937,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389963</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5819,6 +6049,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389938</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5926,6 +6161,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389952</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6033,6 +6273,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389973</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6140,6 +6385,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389985</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6247,6 +6497,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389987</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6363,6 +6618,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389971</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6470,6 +6730,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389972</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6577,6 +6842,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389942</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6703,6 +6973,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389976</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6829,8 +7104,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134389982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>